--- a/public/Quiz2.xlsx
+++ b/public/Quiz2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Micael\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44DC7283-F6BC-4996-8CF9-AD755016A7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C5B196-9373-4710-A238-F58BD3E7F15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{814585D2-DACD-4865-94B7-0CB5BA22B5AF}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="54">
   <si>
     <t>module</t>
   </si>
@@ -60,211 +60,133 @@
     <t>E1</t>
   </si>
   <si>
-    <t>En góndola ves un hueco de tu producto más rotador (A) y, en su lugar, un producto de otro proveedor (C). El cliente está ocupado. ¿Cuál es tu primera acción más inteligente?</t>
-  </si>
-  <si>
-    <t>Preguntar por qué está comprando C a otro proveedor antes de resolver reposición y quiebres de tus productos.</t>
-  </si>
-  <si>
-    <t>Asegurar reposición de A para no perder ventas y, con eso cubierto, abrir la conversación sobre el frente de C.</t>
-  </si>
-  <si>
-    <t>Pedirle que saque C de la góndola y te dé ese frente, sin revisar rotación ni motivo de la elección.</t>
-  </si>
-  <si>
-    <t>Dejar el quiebre de A para después y arrancar mostrando promos generales para sumar volumen hoy.</t>
-  </si>
-  <si>
-    <t>Abrir la charla por logística/entregas antes de resolver el faltante visible en góndola y su impacto.</t>
-  </si>
-  <si>
     <t>E2</t>
   </si>
   <si>
-    <t>Ves un producto tuyo bien ubicado pero sin precio visible. Cual accion se alinea mejor al rol?</t>
-  </si>
-  <si>
-    <t>No decir nada: asumir que el cliente ya sabe el precio y que eso no afecta la decisión de compra.</t>
-  </si>
-  <si>
-    <t>Sugerir poner precio visible y, si corresponde, un cartel simple para facilitar la venta y la rotación.</t>
-  </si>
-  <si>
-    <t>Cambiar vos mismo el precio con una etiqueta nueva, aunque no corresponda. Para dejar una salida concreta.</t>
-  </si>
-  <si>
-    <t>Sacar el producto del frente para que no se note, y después ver si lo reubicás en otro lado.</t>
-  </si>
-  <si>
-    <t>Usar ese detalle para presionarlo a comprar más. Para ordenar el foco y avanzar.</t>
-  </si>
-  <si>
     <t>E3</t>
   </si>
   <si>
-    <t>El cliente te dice: “La entrega anterior llegó tarde”. Cual respuesta te mantiene profesional y te devuelve rapido al foco comercial?</t>
-  </si>
-  <si>
-    <t>Entiendo, gracias por avisarme. Lo registro para que se corrija. Para no perder ventas hoy: ¿cómo venís de stock y reposición?</t>
-  </si>
-  <si>
-    <t>Sí, tenés razón, no vuelve a pasar; te explico rápido qué pasó y cómo se corrige.</t>
-  </si>
-  <si>
-    <t>No fue culpa mía; si tu encargado pidió tarde o el depósito se demoró, no es tema mío.</t>
-  </si>
-  <si>
-    <t>Contame bien: qué hora, quién recibió, qué remito y qué faltó, y lo vemos ahora.</t>
-  </si>
-  <si>
-    <t>Eso no lo manejo yo, yo solo vendo. Para que quede corto y claro.</t>
-  </si>
-  <si>
     <t>E4</t>
   </si>
   <si>
-    <t>El Bot muestra que normalmente compra 5 cajas por semana de un producto. En heladera quedan 2 unidades. Cual propuesta de reposicion es mas ordenada?</t>
-  </si>
-  <si>
-    <t>“Veo que venís en 5 cajas por semana y hoy te quedan 2 unidades; ¿reponemos 5 para cubrir esta semana?”</t>
-  </si>
-  <si>
-    <t>“Decime qué te gustaría llevar hoy y lo armamos sobre la marcha con lo que te parezca.”</t>
-  </si>
-  <si>
-    <t>“Aprovechemos y llevemos 15 cajas así te olvidás por un tiempo y no te preocupás después.”</t>
-  </si>
-  <si>
-    <t>“Si te quedó poco, mejor no repongas por ahora y lo revisamos más adelante en otra visita.”</t>
-  </si>
-  <si>
-    <t>“Te dejo el catálogo para que lo mires y después lo vemos con más tiempo cuando estés más tranquilo.”</t>
-  </si>
-  <si>
     <t>E5</t>
   </si>
   <si>
-    <t>Detectas un producto tuyo clavado (mismo nivel de stock hace semanas). Que enfoque de reposicion es mas inteligente?</t>
-  </si>
-  <si>
-    <t>“Sumemos un poco más del mismo para darle más presencia y ver si se mueve por volumen.”</t>
-  </si>
-  <si>
-    <t>“Dejémoslo como está y sigamos con el pedido habitual, sin meternos en ese producto hoy.”</t>
-  </si>
-  <si>
-    <t>“Antes de reponer, ubiquemos qué lo frena: salida, precio o ubicación, y definimos un ajuste puntual.”</t>
-  </si>
-  <si>
-    <t>“Esto lo compraste mal; así no se trabaja. La próxima pedime solo lo que rota bien.”</t>
-  </si>
-  <si>
-    <t>“Después lo vemos; por ahora sigamos con otra cosa y cerramos el pedido como siempre hoy.”</t>
-  </si>
-  <si>
     <t>E6</t>
   </si>
   <si>
-    <t>Despues de asegurar reposicion, queres entender por que el cliente compra una categoria a otro proveedor. Que pregunta cuida mejor el vinculo?</t>
-  </si>
-  <si>
-    <t>¿Por qué le comprás a otro si yo también te lo puedo vender hoy mismo acá?</t>
-  </si>
-  <si>
-    <t>¿Ese proveedor te da mejor precio? Si no, te conviene comprarme a mí esta vez hoy.</t>
-  </si>
-  <si>
-    <t>¿Qué te gusta más de ese proveedor: precio, entrega o surtido, para entender tu elección mejor?</t>
-  </si>
-  <si>
-    <t>¿Qué te viene resolviendo ese proveedor en esa categoría, para ver cómo me ajusto yo también?</t>
-  </si>
-  <si>
-    <t>Si preferís, no lo hablamos ahora; seguimos con lo de siempre y cerramos tranquilo hoy acá.</t>
-  </si>
-  <si>
     <t>E7</t>
   </si>
   <si>
-    <t>Ves que el precio en gondola de tu producto esta muy por encima de lo habitual del barrio. Que accion es mas alineada al foco en venta?</t>
-  </si>
-  <si>
-    <t>“Lo dejo como está; el precio lo maneja el local y no me meto con eso hoy.”</t>
-  </si>
-  <si>
-    <t>“Lo bajo yo ahora mismo para que se venda, y después vemos el resto cuando haya tiempo.”</t>
-  </si>
-  <si>
-    <t>“Ese precio está mal; así no vas a vender” y lo marco como error sin preguntar contexto.</t>
-  </si>
-  <si>
-    <t>“Llevemos más cantidad igual para compensar” y después vemos si se mueve con volumen ahí.</t>
-  </si>
-  <si>
-    <t>“¿A cuánto lo estás vendiendo hoy?” para entender el punto de partida antes de proponer ajuste.</t>
-  </si>
-  <si>
     <t>E8</t>
   </si>
   <si>
-    <t>Que tema NO deberias abrir vos durante la recorrida si el cliente no lo menciona?</t>
-  </si>
-  <si>
-    <t>Faltantes de stock o quiebres en góndola que puedan estar frenando ventas hoy.</t>
-  </si>
-  <si>
-    <t>Productos que no rotan o están clavados y ocupan espacio sin aportar margen.</t>
-  </si>
-  <si>
-    <t>Precio visible en góndola si está fuera de rango para el barrio o la rotación.</t>
-  </si>
-  <si>
-    <t>Problemas de logística o entregas como tema principal, sin señal previa del cliente.</t>
-  </si>
-  <si>
-    <t>Productos de otros proveedores en la categoría y cómo conviven con tus frentes actuales.</t>
-  </si>
-  <si>
     <t>E9</t>
   </si>
   <si>
-    <t>Tenes 3 minutos para recorrer. Que chequeo te da mas informacion para armar un pedido base con sentido?</t>
-  </si>
-  <si>
-    <t>Chequear faltantes y quiebres de lo que más rota para armar la reposición base del local hoy.</t>
-  </si>
-  <si>
-    <t>Detectar qué productos están clavados y qué conviene pausar, sin mirar el resto del recorrido.</t>
-  </si>
-  <si>
-    <t>Revisar precios visibles en góndola para ver desvíos, sin mirar rotación ni faltantes del local.</t>
-  </si>
-  <si>
-    <t>Abrir por entregas y servicio para ver reclamos, antes de revisar stock en punto de venta.</t>
-  </si>
-  <si>
-    <t>Mirar el triángulo: vendido, no vendido y competencia, para armar base y una oportunidad real.</t>
-  </si>
-  <si>
     <t>E10</t>
   </si>
   <si>
-    <t>Cual frase propone reposicion base sin marear al cliente?</t>
-  </si>
-  <si>
-    <t>Si querés, decime qué te falta hoy y lo armamos rápido con eso.</t>
-  </si>
-  <si>
-    <t>Te muestro algunas opciones y vos vas eligiendo de a poco lo que prefieras.</t>
-  </si>
-  <si>
-    <t>Veo que de X estás corto; para cubrir la semana te propongo reponer 5 cajas hoy.</t>
-  </si>
-  <si>
-    <t>Hoy te recomiendo sumar algunos lanzamientos que están saliendo y probarlos esta semana.</t>
-  </si>
-  <si>
-    <t>Necesito que hoy el pedido sea más grande para que me cierre bien la visita. Respuestas + explicacion (por que es correcta)</t>
+    <t>Vino $1500 / costo $1000 ¿Ganancia?</t>
+  </si>
+  <si>
+    <t>$300</t>
+  </si>
+  <si>
+    <t>$400</t>
+  </si>
+  <si>
+    <t>$500</t>
+  </si>
+  <si>
+    <t>$600</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Hamburguesa $4000 / costo $2000 ¿Markup?</t>
+  </si>
+  <si>
+    <t>50%</t>
+  </si>
+  <si>
+    <t>75%</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>200%</t>
+  </si>
+  <si>
+    <t>Salchichas $900 / costo $600 ¿Ganancia?</t>
+  </si>
+  <si>
+    <t>$200</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Papel higiénico $1000 / costo $800 ¿Markup?</t>
+  </si>
+  <si>
+    <t>20%</t>
+  </si>
+  <si>
+    <t>25%</t>
+  </si>
+  <si>
+    <t>40%</t>
+  </si>
+  <si>
+    <t>Pañales $6000 / costo $4000 ¿Ganancia?</t>
+  </si>
+  <si>
+    <t>$1000</t>
+  </si>
+  <si>
+    <t>$1500</t>
+  </si>
+  <si>
+    <t>$2000</t>
+  </si>
+  <si>
+    <t>$2500</t>
+  </si>
+  <si>
+    <t>Gaseosa $1200 / costo $900 ¿Markup?</t>
+  </si>
+  <si>
+    <t>33%</t>
+  </si>
+  <si>
+    <t>Galletitas $1000 / costo $500 ¿Ganancia?</t>
+  </si>
+  <si>
+    <t>$250</t>
+  </si>
+  <si>
+    <t>Helado $1600 / costo $1200 ¿Markup?</t>
+  </si>
+  <si>
+    <t>Agua $750 / costo $600 ¿Ganancia?</t>
+  </si>
+  <si>
+    <t>$100</t>
+  </si>
+  <si>
+    <t>$150</t>
+  </si>
+  <si>
+    <t>Chocolate $1500 / costo $900 ¿Markup?</t>
+  </si>
+  <si>
+    <t>60%</t>
+  </si>
+  <si>
+    <t>66%</t>
   </si>
 </sst>
 </file>
@@ -656,25 +578,25 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
+        <v>24</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -682,28 +604,28 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -711,28 +633,28 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" t="s">
-        <v>30</v>
+        <v>23</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -740,28 +662,28 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
         <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -769,28 +691,28 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
         <v>38</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>39</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>41</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>42</v>
       </c>
-      <c r="G6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" t="s">
-        <v>44</v>
+      <c r="H6">
+        <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -798,28 +720,28 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G7" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" t="s">
-        <v>51</v>
+        <v>27</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -827,28 +749,28 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" t="s">
-        <v>58</v>
+        <v>24</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -856,28 +778,28 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>64</v>
-      </c>
-      <c r="H9" t="s">
-        <v>65</v>
+        <v>27</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -885,28 +807,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="F10" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="G10" t="s">
-        <v>71</v>
-      </c>
-      <c r="H10" t="s">
-        <v>72</v>
+        <v>46</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -914,28 +836,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="F11" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="G11" t="s">
-        <v>78</v>
-      </c>
-      <c r="H11" t="s">
-        <v>79</v>
+        <v>28</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/public/Quiz2.xlsx
+++ b/public/Quiz2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Micael\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C5B196-9373-4710-A238-F58BD3E7F15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F05A1B6B-DABF-4B7F-9FF4-55C570FCA346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{814585D2-DACD-4865-94B7-0CB5BA22B5AF}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="80">
   <si>
     <t>module</t>
   </si>
@@ -54,139 +54,217 @@
     <t>correct</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>E1</t>
-  </si>
-  <si>
-    <t>E2</t>
-  </si>
-  <si>
-    <t>E3</t>
-  </si>
-  <si>
-    <t>E4</t>
-  </si>
-  <si>
-    <t>E5</t>
-  </si>
-  <si>
-    <t>E6</t>
-  </si>
-  <si>
-    <t>E7</t>
-  </si>
-  <si>
-    <t>E8</t>
-  </si>
-  <si>
-    <t>E9</t>
-  </si>
-  <si>
-    <t>E10</t>
-  </si>
-  <si>
-    <t>Vino $1500 / costo $1000 ¿Ganancia?</t>
-  </si>
-  <si>
-    <t>$300</t>
-  </si>
-  <si>
-    <t>$400</t>
-  </si>
-  <si>
-    <t>$500</t>
-  </si>
-  <si>
-    <t>$600</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>Hamburguesa $4000 / costo $2000 ¿Markup?</t>
-  </si>
-  <si>
-    <t>50%</t>
-  </si>
-  <si>
-    <t>75%</t>
-  </si>
-  <si>
-    <t>100%</t>
-  </si>
-  <si>
-    <t>200%</t>
-  </si>
-  <si>
-    <t>Salchichas $900 / costo $600 ¿Ganancia?</t>
-  </si>
-  <si>
-    <t>$200</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>Papel higiénico $1000 / costo $800 ¿Markup?</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>40%</t>
-  </si>
-  <si>
-    <t>Pañales $6000 / costo $4000 ¿Ganancia?</t>
-  </si>
-  <si>
-    <t>$1000</t>
-  </si>
-  <si>
-    <t>$1500</t>
-  </si>
-  <si>
-    <t>$2000</t>
-  </si>
-  <si>
-    <t>$2500</t>
-  </si>
-  <si>
-    <t>Gaseosa $1200 / costo $900 ¿Markup?</t>
-  </si>
-  <si>
-    <t>33%</t>
-  </si>
-  <si>
-    <t>Galletitas $1000 / costo $500 ¿Ganancia?</t>
-  </si>
-  <si>
-    <t>$250</t>
-  </si>
-  <si>
-    <t>Helado $1600 / costo $1200 ¿Markup?</t>
-  </si>
-  <si>
-    <t>Agua $750 / costo $600 ¿Ganancia?</t>
-  </si>
-  <si>
-    <t>$100</t>
-  </si>
-  <si>
-    <t>$150</t>
-  </si>
-  <si>
-    <t>Chocolate $1500 / costo $900 ¿Markup?</t>
-  </si>
-  <si>
-    <t>60%</t>
-  </si>
-  <si>
-    <t>66%</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>Estas a punto de entrar y vas tarde. Tenes 45 segundos. Cual preparacion minima te deja mejor parado para no improvisar adentro?</t>
+  </si>
+  <si>
+    <t>Entrar directo y preguntar “¿qué te anoto?” para ahorrar tiempo, sin preparar nada afuera.</t>
+  </si>
+  <si>
+    <t>Mirar solo promos generales y entrar a ofrecerlas, para no meter presión ni discutir.</t>
+  </si>
+  <si>
+    <t>Marcar GPS, mirar en Bot/App 2 datos (compra fija + última compra) y entrar con plan simple: base + 1 idea.</t>
+  </si>
+  <si>
+    <t>Pensar una estrategia sin mirar Bot/App: “adentro veo” y arrancar. Y seguís con el pedido en el sistema.</t>
+  </si>
+  <si>
+    <t>Llamar al cliente antes de entrar para preguntarle qué quiere y armar el pedido por teléfono.</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>En el Bot ves que un cliente que siempre compraba un producto fuerte bajo mucho el volumen las ultimas 2 visitas. Que preparación es más inteligente antes de entrar?</t>
+  </si>
+  <si>
+    <t>Ignorarlo y sostener la visita igual, asumiendo que ya no le interesa ese producto.</t>
+  </si>
+  <si>
+    <t>Entrar ofreciendo solo productos nuevos para subir ticket, sin revisar qué pasó con el fuerte.</t>
+  </si>
+  <si>
+    <t>Preparar una pregunta corta para entender el motivo (rotación/precio/competencia) y ajustar reposición a su realidad.</t>
+  </si>
+  <si>
+    <t>Entrar a reclamarle por qué bajó y presionarlo para que vuelva a subir el volumen.</t>
+  </si>
+  <si>
+    <t>No visitarlo por ahora, asumir que no vale la pena y pasar al siguiente cliente hoy.</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>Cual de estas cosas NO es parte del checklist de preparacion inmediata antes de entrar?</t>
+  </si>
+  <si>
+    <t>Marcar GPS al llegar. Para no meter presión ni discutir.</t>
+  </si>
+  <si>
+    <t>Revisar qué compra siempre, cantidades y frecuencia. Para que quede corto y claro.</t>
+  </si>
+  <si>
+    <t>Identificar si compra categorías del portfolio a otros proveedores.</t>
+  </si>
+  <si>
+    <t>Memorizar una lista completa de 10 promos para decirlas todas</t>
+  </si>
+  <si>
+    <t>Recordar su problema principal de la visita anterior.</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>Cliente nuevo sin historial. Cual seria una preparacion minima aceptable antes de entrar?</t>
+  </si>
+  <si>
+    <t>Entrar sin preparar nada y empezar la conversación “a ver qué sale” en el momento.</t>
+  </si>
+  <si>
+    <t>Marcar GPS, revisar ofertas zonales y armar un pedido base típico más una pregunta de diagnóstico.</t>
+  </si>
+  <si>
+    <t>Marcar GPS y confiar en improvisar todo adentro, sin revisar información previa del recorrido.</t>
+  </si>
+  <si>
+    <t>Entrar con un discurso de promos generales y esperar que alguna alternativa le interese hoy.</t>
+  </si>
+  <si>
+    <t>Postergar la visita hasta tener compras registradas y recién ahí empezar a trabajarlo en serio.</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>Tenes 6 promos activas. En el Bot ves que el cliente viene quejandose de margen. Que decision previa es mas solida?</t>
+  </si>
+  <si>
+    <t>Entrar y recitar las 6 promos seguidas, esperando que alguna le cierre en el momento.</t>
+  </si>
+  <si>
+    <t>Elegir la promo más fuerte del mes, aunque no conecte con el problema de margen del cliente.</t>
+  </si>
+  <si>
+    <t>Evitar promos por completo y limitarte a tomar el pedido habitual sin proponer alternativas.</t>
+  </si>
+  <si>
+    <t>Seleccionar 1–2 promos que mejoren margen y preparar una frase simple de beneficio para ese cliente.</t>
+  </si>
+  <si>
+    <t>Ofrecer solo lanzamientos nuevos y dejar afuera promos pensadas para margen y rotación del local.</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>Antes de entrar, recordas que el cliente te dijo la visita pasada: 'no tengo mas lugar'. Que mini estrategia pre-armas?</t>
+  </si>
+  <si>
+    <t>Entrar con foco en subir volumen para aprovechar el viaje, aunque ya avisó que no tiene espacio.</t>
+  </si>
+  <si>
+    <t>Entrar con foco en liberar espacio: ver qué no rota y proponer alta rotación en pocas unidades y formato chico.</t>
+  </si>
+  <si>
+    <t>No ofrecer nada nuevo y pedir solo “lo de siempre”, aunque la traba de espacio siga igual.</t>
+  </si>
+  <si>
+    <t>Cambiar el tema hacia impuestos y desviar la conversación, sin resolver la traba principal del cliente.</t>
+  </si>
+  <si>
+    <t>Evitar mirar depósito/estantería para no incomodar y seguir la visita como si no hubiera problema.</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>Te diste cuenta de que entraste sin marcar GPS. Que accion es mas profesional?</t>
+  </si>
+  <si>
+    <t>Marcar GPS apenas puedas (si hace falta, salir un segundo a la puerta) para que la visita quede registrada.</t>
+  </si>
+  <si>
+    <t>Seguir la visita normal sin marcar GPS y darlo por perdido en esta vuelta.</t>
+  </si>
+  <si>
+    <t>Marcar el GPS al final del día desde cualquier lugar, solo para que figure en el sistema.</t>
+  </si>
+  <si>
+    <t>Pedirle al cliente que confirme que estuviste y usar eso como reemplazo del GPS.</t>
+  </si>
+  <si>
+    <t>Marcar GPS en el negocio siguiente “para compensar” y cerrar el número de visitas.</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>Ordena la secuencia mas logica antes de entrar (1 minuto de preparacion).</t>
+  </si>
+  <si>
+    <t>Marcar GPS -&gt; mirar Bot/App -&gt; pensar 1–2 ideas -&gt; entrar y saludar con foco.</t>
+  </si>
+  <si>
+    <t>Entrar y saludar -&gt; marcar GPS -&gt; mirar Bot/App -&gt; pensar estrategia ya adentro.</t>
+  </si>
+  <si>
+    <t>Mirar Bot/App -&gt; entrar y saludar -&gt; marcar GPS -&gt; pensar estrategia a mitad de visita.</t>
+  </si>
+  <si>
+    <t>Pensar estrategia -&gt; entrar y saludar -&gt; mirar Bot/App -&gt; marcar GPS al final.</t>
+  </si>
+  <si>
+    <t>Marcar GPS -&gt; entrar -&gt; pensar estrategia sin mirar Bot/App y salir improvisando.</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>Cual de estas senales en el Bot/App deberia prenderte una luz para preparar la visita con mas cuidado?</t>
+  </si>
+  <si>
+    <t>Compra siempre lo mismo con la misma frecuencia, y todo viene estable, sin cambios grandes.</t>
+  </si>
+  <si>
+    <t>Tiene pedidos regulares y un comportamiento parejo, sin cambios relevantes. Para seguir con la visita con orden.</t>
+  </si>
+  <si>
+    <t>Tiene histórico corto pero constante, sin variaciones fuertes, y mantiene el mismo patrón.</t>
+  </si>
+  <si>
+    <t>No tiene promos activas hoy, pero su compra viene normal y no hay alertas de caída.</t>
+  </si>
+  <si>
+    <t>Bajó de golpe un producto que antes rotaba bien, y se repitió en las últimas dos visitas.</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>Cual de estas notas de pre-visita es la mas util (1 renglon) para entrar con plan?</t>
+  </si>
+  <si>
+    <t>“Repasar qué rotó la última visita y entrar con 1 pregunta corta para entender qué cambió.”</t>
+  </si>
+  <si>
+    <t>“Priorizar 2 promos que encajen con su compra habitual y mencionarlas si aparece la oportunidad.”</t>
+  </si>
+  <si>
+    <t>“Repasar caballitos X e Y y chequear si hay quiebre/stock para ajustar reposición sin inflar.”</t>
+  </si>
+  <si>
+    <t>“Entrar a escuchar primero y, según lo que diga, armar una propuesta simple en el momento.”</t>
+  </si>
+  <si>
+    <t>“Repongo X e Y (caballitos) + propongo prueba acotada para margen o ahorro de viajes hoy.” Respuestas + explicacion (por que es correcta)</t>
   </si>
 </sst>
 </file>
@@ -578,25 +656,25 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -604,28 +682,28 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -633,28 +711,28 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -662,28 +740,28 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
         <v>34</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>35</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>36</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>37</v>
       </c>
-      <c r="G5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -691,28 +769,28 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="H6" t="s">
+        <v>44</v>
       </c>
       <c r="I6" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -720,28 +798,28 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="H7" t="s">
+        <v>51</v>
       </c>
       <c r="I7" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -749,28 +827,28 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="G8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="H8" t="s">
+        <v>58</v>
       </c>
       <c r="I8" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -778,28 +856,28 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
+        <v>64</v>
+      </c>
+      <c r="H9" t="s">
+        <v>65</v>
       </c>
       <c r="I9" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -807,28 +885,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="G10" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
+        <v>71</v>
+      </c>
+      <c r="H10" t="s">
+        <v>72</v>
       </c>
       <c r="I10" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -836,28 +914,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
+        <v>78</v>
+      </c>
+      <c r="H11" t="s">
+        <v>79</v>
       </c>
       <c r="I11" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/public/Quiz2.xlsx
+++ b/public/Quiz2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Micael\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F05A1B6B-DABF-4B7F-9FF4-55C570FCA346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21124AA9-CD68-4F27-A188-56D064260AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{814585D2-DACD-4865-94B7-0CB5BA22B5AF}"/>
   </bookViews>
@@ -54,217 +54,217 @@
     <t>correct</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>Estas a punto de entrar y vas tarde. Tenes 45 segundos. Cual preparacion minima te deja mejor parado para no improvisar adentro?</t>
-  </si>
-  <si>
-    <t>Entrar directo y preguntar “¿qué te anoto?” para ahorrar tiempo, sin preparar nada afuera.</t>
-  </si>
-  <si>
-    <t>Mirar solo promos generales y entrar a ofrecerlas, para no meter presión ni discutir.</t>
-  </si>
-  <si>
-    <t>Marcar GPS, mirar en Bot/App 2 datos (compra fija + última compra) y entrar con plan simple: base + 1 idea.</t>
-  </si>
-  <si>
-    <t>Pensar una estrategia sin mirar Bot/App: “adentro veo” y arrancar. Y seguís con el pedido en el sistema.</t>
-  </si>
-  <si>
-    <t>Llamar al cliente antes de entrar para preguntarle qué quiere y armar el pedido por teléfono.</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>En el Bot ves que un cliente que siempre compraba un producto fuerte bajo mucho el volumen las ultimas 2 visitas. Que preparación es más inteligente antes de entrar?</t>
-  </si>
-  <si>
-    <t>Ignorarlo y sostener la visita igual, asumiendo que ya no le interesa ese producto.</t>
-  </si>
-  <si>
-    <t>Entrar ofreciendo solo productos nuevos para subir ticket, sin revisar qué pasó con el fuerte.</t>
-  </si>
-  <si>
-    <t>Preparar una pregunta corta para entender el motivo (rotación/precio/competencia) y ajustar reposición a su realidad.</t>
-  </si>
-  <si>
-    <t>Entrar a reclamarle por qué bajó y presionarlo para que vuelva a subir el volumen.</t>
-  </si>
-  <si>
-    <t>No visitarlo por ahora, asumir que no vale la pena y pasar al siguiente cliente hoy.</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>Cual de estas cosas NO es parte del checklist de preparacion inmediata antes de entrar?</t>
-  </si>
-  <si>
-    <t>Marcar GPS al llegar. Para no meter presión ni discutir.</t>
-  </si>
-  <si>
-    <t>Revisar qué compra siempre, cantidades y frecuencia. Para que quede corto y claro.</t>
-  </si>
-  <si>
-    <t>Identificar si compra categorías del portfolio a otros proveedores.</t>
-  </si>
-  <si>
-    <t>Memorizar una lista completa de 10 promos para decirlas todas</t>
-  </si>
-  <si>
-    <t>Recordar su problema principal de la visita anterior.</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>Cliente nuevo sin historial. Cual seria una preparacion minima aceptable antes de entrar?</t>
-  </si>
-  <si>
-    <t>Entrar sin preparar nada y empezar la conversación “a ver qué sale” en el momento.</t>
-  </si>
-  <si>
-    <t>Marcar GPS, revisar ofertas zonales y armar un pedido base típico más una pregunta de diagnóstico.</t>
-  </si>
-  <si>
-    <t>Marcar GPS y confiar en improvisar todo adentro, sin revisar información previa del recorrido.</t>
-  </si>
-  <si>
-    <t>Entrar con un discurso de promos generales y esperar que alguna alternativa le interese hoy.</t>
-  </si>
-  <si>
-    <t>Postergar la visita hasta tener compras registradas y recién ahí empezar a trabajarlo en serio.</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>Tenes 6 promos activas. En el Bot ves que el cliente viene quejandose de margen. Que decision previa es mas solida?</t>
-  </si>
-  <si>
-    <t>Entrar y recitar las 6 promos seguidas, esperando que alguna le cierre en el momento.</t>
-  </si>
-  <si>
-    <t>Elegir la promo más fuerte del mes, aunque no conecte con el problema de margen del cliente.</t>
-  </si>
-  <si>
-    <t>Evitar promos por completo y limitarte a tomar el pedido habitual sin proponer alternativas.</t>
-  </si>
-  <si>
-    <t>Seleccionar 1–2 promos que mejoren margen y preparar una frase simple de beneficio para ese cliente.</t>
-  </si>
-  <si>
-    <t>Ofrecer solo lanzamientos nuevos y dejar afuera promos pensadas para margen y rotación del local.</t>
-  </si>
-  <si>
-    <t>C6</t>
-  </si>
-  <si>
-    <t>Antes de entrar, recordas que el cliente te dijo la visita pasada: 'no tengo mas lugar'. Que mini estrategia pre-armas?</t>
-  </si>
-  <si>
-    <t>Entrar con foco en subir volumen para aprovechar el viaje, aunque ya avisó que no tiene espacio.</t>
-  </si>
-  <si>
-    <t>Entrar con foco en liberar espacio: ver qué no rota y proponer alta rotación en pocas unidades y formato chico.</t>
-  </si>
-  <si>
-    <t>No ofrecer nada nuevo y pedir solo “lo de siempre”, aunque la traba de espacio siga igual.</t>
-  </si>
-  <si>
-    <t>Cambiar el tema hacia impuestos y desviar la conversación, sin resolver la traba principal del cliente.</t>
-  </si>
-  <si>
-    <t>Evitar mirar depósito/estantería para no incomodar y seguir la visita como si no hubiera problema.</t>
-  </si>
-  <si>
-    <t>C7</t>
-  </si>
-  <si>
-    <t>Te diste cuenta de que entraste sin marcar GPS. Que accion es mas profesional?</t>
-  </si>
-  <si>
-    <t>Marcar GPS apenas puedas (si hace falta, salir un segundo a la puerta) para que la visita quede registrada.</t>
-  </si>
-  <si>
-    <t>Seguir la visita normal sin marcar GPS y darlo por perdido en esta vuelta.</t>
-  </si>
-  <si>
-    <t>Marcar el GPS al final del día desde cualquier lugar, solo para que figure en el sistema.</t>
-  </si>
-  <si>
-    <t>Pedirle al cliente que confirme que estuviste y usar eso como reemplazo del GPS.</t>
-  </si>
-  <si>
-    <t>Marcar GPS en el negocio siguiente “para compensar” y cerrar el número de visitas.</t>
-  </si>
-  <si>
-    <t>C8</t>
-  </si>
-  <si>
-    <t>Ordena la secuencia mas logica antes de entrar (1 minuto de preparacion).</t>
-  </si>
-  <si>
-    <t>Marcar GPS -&gt; mirar Bot/App -&gt; pensar 1–2 ideas -&gt; entrar y saludar con foco.</t>
-  </si>
-  <si>
-    <t>Entrar y saludar -&gt; marcar GPS -&gt; mirar Bot/App -&gt; pensar estrategia ya adentro.</t>
-  </si>
-  <si>
-    <t>Mirar Bot/App -&gt; entrar y saludar -&gt; marcar GPS -&gt; pensar estrategia a mitad de visita.</t>
-  </si>
-  <si>
-    <t>Pensar estrategia -&gt; entrar y saludar -&gt; mirar Bot/App -&gt; marcar GPS al final.</t>
-  </si>
-  <si>
-    <t>Marcar GPS -&gt; entrar -&gt; pensar estrategia sin mirar Bot/App y salir improvisando.</t>
-  </si>
-  <si>
-    <t>C9</t>
-  </si>
-  <si>
-    <t>Cual de estas senales en el Bot/App deberia prenderte una luz para preparar la visita con mas cuidado?</t>
-  </si>
-  <si>
-    <t>Compra siempre lo mismo con la misma frecuencia, y todo viene estable, sin cambios grandes.</t>
-  </si>
-  <si>
-    <t>Tiene pedidos regulares y un comportamiento parejo, sin cambios relevantes. Para seguir con la visita con orden.</t>
-  </si>
-  <si>
-    <t>Tiene histórico corto pero constante, sin variaciones fuertes, y mantiene el mismo patrón.</t>
-  </si>
-  <si>
-    <t>No tiene promos activas hoy, pero su compra viene normal y no hay alertas de caída.</t>
-  </si>
-  <si>
-    <t>Bajó de golpe un producto que antes rotaba bien, y se repitió en las últimas dos visitas.</t>
-  </si>
-  <si>
-    <t>C10</t>
-  </si>
-  <si>
-    <t>Cual de estas notas de pre-visita es la mas util (1 renglon) para entrar con plan?</t>
-  </si>
-  <si>
-    <t>“Repasar qué rotó la última visita y entrar con 1 pregunta corta para entender qué cambió.”</t>
-  </si>
-  <si>
-    <t>“Priorizar 2 promos que encajen con su compra habitual y mencionarlas si aparece la oportunidad.”</t>
-  </si>
-  <si>
-    <t>“Repasar caballitos X e Y y chequear si hay quiebre/stock para ajustar reposición sin inflar.”</t>
-  </si>
-  <si>
-    <t>“Entrar a escuchar primero y, según lo que diga, armar una propuesta simple en el momento.”</t>
-  </si>
-  <si>
-    <t>“Repongo X e Y (caballitos) + propongo prueba acotada para margen o ahorro de viajes hoy.” Respuestas + explicacion (por que es correcta)</t>
+    <t>6</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>Cliente: “Vendo, pero no me queda nada”. En que tipo de dolor cae principalmente?</t>
+  </si>
+  <si>
+    <t>Dolor de ventas: vende “algo”, pero siente que no alcanza volumen, como si el movimiento no compensara el esfuerzo del día.</t>
+  </si>
+  <si>
+    <t>Dolor de rentabilidad/margen: hay venta, pero la ganancia por operación es baja y “no queda nada” al final, aunque entre plata.</t>
+  </si>
+  <si>
+    <t>Dolor de tiempo/cansancio: vende y trabaja. Para dejar una salida concreta. Para no entrar en detalles de más.</t>
+  </si>
+  <si>
+    <t>Dolor de espacio/stock: vende, pero se le desordena el local, se acumula mercadería o no puede exhibir bien, y eso le come resultado.</t>
+  </si>
+  <si>
+    <t>Comentario general: expresa frustración, pero no permite ubicar si es margen, ventas, tiempo o stock sin una pregunta más.</t>
+  </si>
+  <si>
+    <t>G2</t>
+  </si>
+  <si>
+    <t>Cliente: “No paro nunca, siempre tengo que ir yo al mayorista”. Que pregunta convierte mejor ese comentario en necesidad explicita?</t>
+  </si>
+  <si>
+    <t>“¿Te pasa que preferís hacerlo vos o es que no tenés a quién delegarlo en el local?”</t>
+  </si>
+  <si>
+    <t>“Si pudieras ahorrarte uno o dos viajes al mayorista por mes, ¿eso te resolvería parte del día?”</t>
+  </si>
+  <si>
+    <t>“¿Cuánto te cuesta por semana entre nafta, peajes y el tiempo que perdés en esos viajes?”</t>
+  </si>
+  <si>
+    <t>“¿Qué es lo que te obliga a ir vos: precio, falta de entrega o no tener una reposición armada?”</t>
+  </si>
+  <si>
+    <t>“Entiendo; hoy sigamos con lo de siempre y la próxima lo miramos con más calma.”</t>
+  </si>
+  <si>
+    <t>G3</t>
+  </si>
+  <si>
+    <t>Elegi la mejor pregunta de implicacion para un cliente con stock clavado.</t>
+  </si>
+  <si>
+    <t>“Si ese stock sigue parado 2–3 meses más, ¿qué te termina costando: plata inmovilizada, espacio o perder otras ventas?”.</t>
+  </si>
+  <si>
+    <t>“¿Cuánto espacio de góndola/heladera tenés disponible hoy?”. Para que quede corto y claro.</t>
+  </si>
+  <si>
+    <t>“¿Te convence esta marca o preferís otra?”. Para seguir con la visita con orden.</t>
+  </si>
+  <si>
+    <t>“Cuando vas al mayorista, ¿cada cuánto terminás yendo por semana?”.</t>
+  </si>
+  <si>
+    <t>“¿Hace cuánto lo trabajás y desde cuándo notaste que se clavó?”.</t>
+  </si>
+  <si>
+    <t>G4</t>
+  </si>
+  <si>
+    <t>Cliente: “Tengo el deposito explotado”. Cual frase de empatia es mas alineada?</t>
+  </si>
+  <si>
+    <t>“Te entiendo; a veces pasa cuando se compra sin mirar rotación y después queda todo apretado.”</t>
+  </si>
+  <si>
+    <t>“Te entiendo; es bastante común en estos días, vamos viendo cómo lo acomodamos con calma.”</t>
+  </si>
+  <si>
+    <t>“Te entiendo; con el depósito así se traba todo: no entra reposición, se desordena y se pierden ventas por falta de espacio.”</t>
+  </si>
+  <si>
+    <t>“Te entiendo; no es tan grave, suele acomodarse solo con un poco de orden y tiempo.”</t>
+  </si>
+  <si>
+    <t>“Te entiendo; metamos igual y después lo acomodás, así aprovechamos la visita y no perdés la vuelta.”</t>
+  </si>
+  <si>
+    <t>G5</t>
+  </si>
+  <si>
+    <t>El cliente dice dos cosas: “No se vende” y “no tengo lugar”. Que haria mejor un preventista para definir el foco?</t>
+  </si>
+  <si>
+    <t>“Para ordenar la charla, si tuvieras que elegir una sola: ¿hoy te frena más la venta o el espacio?”</t>
+  </si>
+  <si>
+    <t>“Arranco con una promo puntual para destrabar algo rápido y después vemos lo del lugar.”</t>
+  </si>
+  <si>
+    <t>“Dale, pasame lo de siempre y lo cargo, así no perdemos tiempo en esta visita.”</t>
+  </si>
+  <si>
+    <t>“Antes de eso, contame cómo venís con costos fijos e impuestos este mes, así entiendo el contexto.”</t>
+  </si>
+  <si>
+    <t>“En otros locales se está vendiendo; contame qué estás haciendo distinto acá con la categoría.”</t>
+  </si>
+  <si>
+    <t>G6</t>
+  </si>
+  <si>
+    <t>Mientras el cliente te cuenta su problema, cual conducta va en contra de una buena profundizacion del dolor?</t>
+  </si>
+  <si>
+    <t>Dejarlo terminar y hacer una pregunta corta para ordenar lo que escuchaste.</t>
+  </si>
+  <si>
+    <t>Hacer una pregunta sobre consecuencias para dimensionar el impacto del problema en su negocio.</t>
+  </si>
+  <si>
+    <t>Usar una frase breve de empatía y seguir con una pregunta para entender mejor el punto.</t>
+  </si>
+  <si>
+    <t>Interrumpir para mostrar catálogos y precios y pasar directo a oferta “para ahorrar tiempo”.</t>
+  </si>
+  <si>
+    <t>Repetir con tus palabras lo entendido y confirmar si lo interpretaste bien.</t>
+  </si>
+  <si>
+    <t>G7</t>
+  </si>
+  <si>
+    <t>Cliente: “Vendo, pero no me queda plata. Encima los impuestos me matan”. Elegi la mejor combinacion (pregunta de implicación + frase de empatía) para seguir.</t>
+  </si>
+  <si>
+    <t>Pregunta: ¿Más o menos cuánto se te va en impuestos por mes? + Empatía: Te entiendo, es un golpe cuando el margen ya viene justo.</t>
+  </si>
+  <si>
+    <t>Pregunta: ¿Y qué estás haciendo distinto que antes? + Empatía: A muchos les pasa, hay que aguantar. Para que quede corto y claro.</t>
+  </si>
+  <si>
+    <t>Pregunta: ¿Si subís un poco los precios lo compensás? + Empatía: Tranquilo, se acomoda. Para no entrar en detalles de más.</t>
+  </si>
+  <si>
+    <t>Pregunta: Si seguís con este margen 6 meses más, ¿qué te pasa en el negocio (pagos, reinversión, compras)? + Empatía: Te entiendo, es frustrante trabajar y que no quede.</t>
+  </si>
+  <si>
+    <t>Pregunta: ¿Qué sentís que te pega más: impuestos, costos o precio de compra? + Empatía: Qué bronca, la verdad.</t>
+  </si>
+  <si>
+    <t>G8</t>
+  </si>
+  <si>
+    <t>Despues de una pregunta de implicacion, cual es el paso mas conveniente antes de ofrecer producto?</t>
+  </si>
+  <si>
+    <t>Pasar directo a “te muestro cinco opciones que suelen funcionar”, sin chequear si encaja con lo que reconoció.</t>
+  </si>
+  <si>
+    <t>Hacer un comentario neutro y cambiar de tema, dejando la consecuencia planteada sin siguiente paso.</t>
+  </si>
+  <si>
+    <t>Empezar a hablar de entregas y condiciones, aunque no responda al foco del problema que salió.</t>
+  </si>
+  <si>
+    <t>Ir a “cerrémoslo así” y pedir confirmación del pedido, sin acordar antes qué sería útil.</t>
+  </si>
+  <si>
+    <t>Resumir en una frase, chequear acuerdo y recién ahí proponer una opción alineada al foco.</t>
+  </si>
+  <si>
+    <t>G9</t>
+  </si>
+  <si>
+    <t>Cual de estas frases es un ejemplo de necesidad explicita (no solo queja)?</t>
+  </si>
+  <si>
+    <t>“Estoy cansado” y me está costando sostener el ritmo del local esta semana.</t>
+  </si>
+  <si>
+    <t>“No se vende nada” y siento que la mercadería no se está moviendo como antes.</t>
+  </si>
+  <si>
+    <t>“Necesito un proveedor que me entregue y me ahorre ir al mayorista cada semana.”</t>
+  </si>
+  <si>
+    <t>“Los precios están altos” y así se me complica vender sin perder margen del local.</t>
+  </si>
+  <si>
+    <t>“El barrio está difícil” y cada vez entra menos gente a comprar en estos días.</t>
+  </si>
+  <si>
+    <t>G10</t>
+  </si>
+  <si>
+    <t>El cliente dice rápido: “No paro nunca, tengo que ir yo al mayorista.” Tenés 1 minuto para profundizar sin invadir. ¿Qué micro-pregunta es la más efectiva?</t>
+  </si>
+  <si>
+    <t>“¿Cada cuánto estás yendo al mayorista y en qué momento del día se te complica más hacerlo?”</t>
+  </si>
+  <si>
+    <t>“¿Qué es lo que te obliga a ir vos: precio, falta de entrega o que se te corta la mercadería?”</t>
+  </si>
+  <si>
+    <t>“Cuando vas al mayorista, ¿qué terminás buscando sí o sí para no quedarte corto en la semana?”</t>
+  </si>
+  <si>
+    <t>“¿Te pasa por falta de tiempo o porque no confiás en que te entreguen como corresponde siempre?”</t>
+  </si>
+  <si>
+    <t>“Si pudieras ahorrarte uno o dos viajes al mayorista por mes, ¿eso te resolvería parte del día?” Respuestas + explicacion (por que es correcta)</t>
   </si>
 </sst>
 </file>
@@ -674,7 +674,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -703,7 +703,7 @@
         <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -732,7 +732,7 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -761,7 +761,7 @@
         <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -790,7 +790,7 @@
         <v>44</v>
       </c>
       <c r="I6" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -819,7 +819,7 @@
         <v>51</v>
       </c>
       <c r="I7" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -848,7 +848,7 @@
         <v>58</v>
       </c>
       <c r="I8" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -877,7 +877,7 @@
         <v>65</v>
       </c>
       <c r="I9" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -906,7 +906,7 @@
         <v>72</v>
       </c>
       <c r="I10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">

--- a/public/Quiz2.xlsx
+++ b/public/Quiz2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Micael\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21124AA9-CD68-4F27-A188-56D064260AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FD1753-51E9-4772-890E-2DEBF29F0A43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{814585D2-DACD-4865-94B7-0CB5BA22B5AF}"/>
   </bookViews>
@@ -54,217 +54,217 @@
     <t>correct</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>G1</t>
-  </si>
-  <si>
-    <t>Cliente: “Vendo, pero no me queda nada”. En que tipo de dolor cae principalmente?</t>
-  </si>
-  <si>
-    <t>Dolor de ventas: vende “algo”, pero siente que no alcanza volumen, como si el movimiento no compensara el esfuerzo del día.</t>
-  </si>
-  <si>
-    <t>Dolor de rentabilidad/margen: hay venta, pero la ganancia por operación es baja y “no queda nada” al final, aunque entre plata.</t>
-  </si>
-  <si>
-    <t>Dolor de tiempo/cansancio: vende y trabaja. Para dejar una salida concreta. Para no entrar en detalles de más.</t>
-  </si>
-  <si>
-    <t>Dolor de espacio/stock: vende, pero se le desordena el local, se acumula mercadería o no puede exhibir bien, y eso le come resultado.</t>
-  </si>
-  <si>
-    <t>Comentario general: expresa frustración, pero no permite ubicar si es margen, ventas, tiempo o stock sin una pregunta más.</t>
-  </si>
-  <si>
-    <t>G2</t>
-  </si>
-  <si>
-    <t>Cliente: “No paro nunca, siempre tengo que ir yo al mayorista”. Que pregunta convierte mejor ese comentario en necesidad explicita?</t>
-  </si>
-  <si>
-    <t>“¿Te pasa que preferís hacerlo vos o es que no tenés a quién delegarlo en el local?”</t>
-  </si>
-  <si>
-    <t>“Si pudieras ahorrarte uno o dos viajes al mayorista por mes, ¿eso te resolvería parte del día?”</t>
-  </si>
-  <si>
-    <t>“¿Cuánto te cuesta por semana entre nafta, peajes y el tiempo que perdés en esos viajes?”</t>
-  </si>
-  <si>
-    <t>“¿Qué es lo que te obliga a ir vos: precio, falta de entrega o no tener una reposición armada?”</t>
-  </si>
-  <si>
-    <t>“Entiendo; hoy sigamos con lo de siempre y la próxima lo miramos con más calma.”</t>
-  </si>
-  <si>
-    <t>G3</t>
-  </si>
-  <si>
-    <t>Elegi la mejor pregunta de implicacion para un cliente con stock clavado.</t>
-  </si>
-  <si>
-    <t>“Si ese stock sigue parado 2–3 meses más, ¿qué te termina costando: plata inmovilizada, espacio o perder otras ventas?”.</t>
-  </si>
-  <si>
-    <t>“¿Cuánto espacio de góndola/heladera tenés disponible hoy?”. Para que quede corto y claro.</t>
-  </si>
-  <si>
-    <t>“¿Te convence esta marca o preferís otra?”. Para seguir con la visita con orden.</t>
-  </si>
-  <si>
-    <t>“Cuando vas al mayorista, ¿cada cuánto terminás yendo por semana?”.</t>
-  </si>
-  <si>
-    <t>“¿Hace cuánto lo trabajás y desde cuándo notaste que se clavó?”.</t>
-  </si>
-  <si>
-    <t>G4</t>
-  </si>
-  <si>
-    <t>Cliente: “Tengo el deposito explotado”. Cual frase de empatia es mas alineada?</t>
-  </si>
-  <si>
-    <t>“Te entiendo; a veces pasa cuando se compra sin mirar rotación y después queda todo apretado.”</t>
-  </si>
-  <si>
-    <t>“Te entiendo; es bastante común en estos días, vamos viendo cómo lo acomodamos con calma.”</t>
-  </si>
-  <si>
-    <t>“Te entiendo; con el depósito así se traba todo: no entra reposición, se desordena y se pierden ventas por falta de espacio.”</t>
-  </si>
-  <si>
-    <t>“Te entiendo; no es tan grave, suele acomodarse solo con un poco de orden y tiempo.”</t>
-  </si>
-  <si>
-    <t>“Te entiendo; metamos igual y después lo acomodás, así aprovechamos la visita y no perdés la vuelta.”</t>
-  </si>
-  <si>
-    <t>G5</t>
-  </si>
-  <si>
-    <t>El cliente dice dos cosas: “No se vende” y “no tengo lugar”. Que haria mejor un preventista para definir el foco?</t>
-  </si>
-  <si>
-    <t>“Para ordenar la charla, si tuvieras que elegir una sola: ¿hoy te frena más la venta o el espacio?”</t>
-  </si>
-  <si>
-    <t>“Arranco con una promo puntual para destrabar algo rápido y después vemos lo del lugar.”</t>
-  </si>
-  <si>
-    <t>“Dale, pasame lo de siempre y lo cargo, así no perdemos tiempo en esta visita.”</t>
-  </si>
-  <si>
-    <t>“Antes de eso, contame cómo venís con costos fijos e impuestos este mes, así entiendo el contexto.”</t>
-  </si>
-  <si>
-    <t>“En otros locales se está vendiendo; contame qué estás haciendo distinto acá con la categoría.”</t>
-  </si>
-  <si>
-    <t>G6</t>
-  </si>
-  <si>
-    <t>Mientras el cliente te cuenta su problema, cual conducta va en contra de una buena profundizacion del dolor?</t>
-  </si>
-  <si>
-    <t>Dejarlo terminar y hacer una pregunta corta para ordenar lo que escuchaste.</t>
-  </si>
-  <si>
-    <t>Hacer una pregunta sobre consecuencias para dimensionar el impacto del problema en su negocio.</t>
-  </si>
-  <si>
-    <t>Usar una frase breve de empatía y seguir con una pregunta para entender mejor el punto.</t>
-  </si>
-  <si>
-    <t>Interrumpir para mostrar catálogos y precios y pasar directo a oferta “para ahorrar tiempo”.</t>
-  </si>
-  <si>
-    <t>Repetir con tus palabras lo entendido y confirmar si lo interpretaste bien.</t>
-  </si>
-  <si>
-    <t>G7</t>
-  </si>
-  <si>
-    <t>Cliente: “Vendo, pero no me queda plata. Encima los impuestos me matan”. Elegi la mejor combinacion (pregunta de implicación + frase de empatía) para seguir.</t>
-  </si>
-  <si>
-    <t>Pregunta: ¿Más o menos cuánto se te va en impuestos por mes? + Empatía: Te entiendo, es un golpe cuando el margen ya viene justo.</t>
-  </si>
-  <si>
-    <t>Pregunta: ¿Y qué estás haciendo distinto que antes? + Empatía: A muchos les pasa, hay que aguantar. Para que quede corto y claro.</t>
-  </si>
-  <si>
-    <t>Pregunta: ¿Si subís un poco los precios lo compensás? + Empatía: Tranquilo, se acomoda. Para no entrar en detalles de más.</t>
-  </si>
-  <si>
-    <t>Pregunta: Si seguís con este margen 6 meses más, ¿qué te pasa en el negocio (pagos, reinversión, compras)? + Empatía: Te entiendo, es frustrante trabajar y que no quede.</t>
-  </si>
-  <si>
-    <t>Pregunta: ¿Qué sentís que te pega más: impuestos, costos o precio de compra? + Empatía: Qué bronca, la verdad.</t>
-  </si>
-  <si>
-    <t>G8</t>
-  </si>
-  <si>
-    <t>Despues de una pregunta de implicacion, cual es el paso mas conveniente antes de ofrecer producto?</t>
-  </si>
-  <si>
-    <t>Pasar directo a “te muestro cinco opciones que suelen funcionar”, sin chequear si encaja con lo que reconoció.</t>
-  </si>
-  <si>
-    <t>Hacer un comentario neutro y cambiar de tema, dejando la consecuencia planteada sin siguiente paso.</t>
-  </si>
-  <si>
-    <t>Empezar a hablar de entregas y condiciones, aunque no responda al foco del problema que salió.</t>
-  </si>
-  <si>
-    <t>Ir a “cerrémoslo así” y pedir confirmación del pedido, sin acordar antes qué sería útil.</t>
-  </si>
-  <si>
-    <t>Resumir en una frase, chequear acuerdo y recién ahí proponer una opción alineada al foco.</t>
-  </si>
-  <si>
-    <t>G9</t>
-  </si>
-  <si>
-    <t>Cual de estas frases es un ejemplo de necesidad explicita (no solo queja)?</t>
-  </si>
-  <si>
-    <t>“Estoy cansado” y me está costando sostener el ritmo del local esta semana.</t>
-  </si>
-  <si>
-    <t>“No se vende nada” y siento que la mercadería no se está moviendo como antes.</t>
-  </si>
-  <si>
-    <t>“Necesito un proveedor que me entregue y me ahorre ir al mayorista cada semana.”</t>
-  </si>
-  <si>
-    <t>“Los precios están altos” y así se me complica vender sin perder margen del local.</t>
-  </si>
-  <si>
-    <t>“El barrio está difícil” y cada vez entra menos gente a comprar en estos días.</t>
-  </si>
-  <si>
-    <t>G10</t>
-  </si>
-  <si>
-    <t>El cliente dice rápido: “No paro nunca, tengo que ir yo al mayorista.” Tenés 1 minuto para profundizar sin invadir. ¿Qué micro-pregunta es la más efectiva?</t>
-  </si>
-  <si>
-    <t>“¿Cada cuánto estás yendo al mayorista y en qué momento del día se te complica más hacerlo?”</t>
-  </si>
-  <si>
-    <t>“¿Qué es lo que te obliga a ir vos: precio, falta de entrega o que se te corta la mercadería?”</t>
-  </si>
-  <si>
-    <t>“Cuando vas al mayorista, ¿qué terminás buscando sí o sí para no quedarte corto en la semana?”</t>
-  </si>
-  <si>
-    <t>“¿Te pasa por falta de tiempo o porque no confiás en que te entreguen como corresponde siempre?”</t>
-  </si>
-  <si>
-    <t>“Si pudieras ahorrarte uno o dos viajes al mayorista por mes, ¿eso te resolvería parte del día?” Respuestas + explicacion (por que es correcta)</t>
+    <t>4</t>
+  </si>
+  <si>
+    <t>E1</t>
+  </si>
+  <si>
+    <t>En góndola ves un hueco de tu producto más rotador (A) y, en su lugar, un producto de otro proveedor (C). El cliente está ocupado. ¿Cuál es tu primera acción más inteligente?</t>
+  </si>
+  <si>
+    <t>Preguntar por qué está comprando C a otro proveedor antes de resolver reposición y quiebres de tus productos.</t>
+  </si>
+  <si>
+    <t>Asegurar reposición de A para no perder ventas y, con eso cubierto, abrir la conversación sobre el frente de C.</t>
+  </si>
+  <si>
+    <t>Pedirle que saque C de la góndola y te dé ese frente, sin revisar rotación ni motivo de la elección.</t>
+  </si>
+  <si>
+    <t>Dejar el quiebre de A para después y arrancar mostrando promos generales para sumar volumen hoy.</t>
+  </si>
+  <si>
+    <t>Abrir la charla por logística/entregas antes de resolver el faltante visible en góndola y su impacto.</t>
+  </si>
+  <si>
+    <t>E2</t>
+  </si>
+  <si>
+    <t>Ves un producto tuyo bien ubicado pero sin precio visible. Cual accion se alinea mejor al rol?</t>
+  </si>
+  <si>
+    <t>No decir nada: asumir que el cliente ya sabe el precio y que eso no afecta la decisión de compra.</t>
+  </si>
+  <si>
+    <t>Sugerir poner precio visible y, si corresponde, un cartel simple para facilitar la venta y la rotación.</t>
+  </si>
+  <si>
+    <t>Cambiar vos mismo el precio con una etiqueta nueva, aunque no corresponda. Para dejar una salida concreta.</t>
+  </si>
+  <si>
+    <t>Sacar el producto del frente para que no se note, y después ver si lo reubicás en otro lado.</t>
+  </si>
+  <si>
+    <t>Usar ese detalle para presionarlo a comprar más. Para ordenar el foco y avanzar.</t>
+  </si>
+  <si>
+    <t>E3</t>
+  </si>
+  <si>
+    <t>El cliente te dice: “La entrega anterior llegó tarde”. Cual respuesta te mantiene profesional y te devuelve rapido al foco comercial?</t>
+  </si>
+  <si>
+    <t>Entiendo, gracias por avisarme. Lo registro para que se corrija. Para no perder ventas hoy: ¿cómo venís de stock y reposición?</t>
+  </si>
+  <si>
+    <t>Sí, tenés razón, no vuelve a pasar; te explico rápido qué pasó y cómo se corrige.</t>
+  </si>
+  <si>
+    <t>No fue culpa mía; si tu encargado pidió tarde o el depósito se demoró, no es tema mío.</t>
+  </si>
+  <si>
+    <t>Contame bien: qué hora, quién recibió, qué remito y qué faltó, y lo vemos ahora.</t>
+  </si>
+  <si>
+    <t>Eso no lo manejo yo, yo solo vendo. Para que quede corto y claro.</t>
+  </si>
+  <si>
+    <t>E4</t>
+  </si>
+  <si>
+    <t>El Bot muestra que normalmente compra 5 cajas por semana de un producto. En heladera quedan 2 unidades. Cual propuesta de reposicion es mas ordenada?</t>
+  </si>
+  <si>
+    <t>“Veo que venís en 5 cajas por semana y hoy te quedan 2 unidades; ¿reponemos 5 para cubrir esta semana?”</t>
+  </si>
+  <si>
+    <t>“Decime qué te gustaría llevar hoy y lo armamos sobre la marcha con lo que te parezca.”</t>
+  </si>
+  <si>
+    <t>“Aprovechemos y llevemos 15 cajas así te olvidás por un tiempo y no te preocupás después.”</t>
+  </si>
+  <si>
+    <t>“Si te quedó poco, mejor no repongas por ahora y lo revisamos más adelante en otra visita.”</t>
+  </si>
+  <si>
+    <t>“Te dejo el catálogo para que lo mires y después lo vemos con más tiempo cuando estés más tranquilo.”</t>
+  </si>
+  <si>
+    <t>E5</t>
+  </si>
+  <si>
+    <t>Detectas un producto tuyo clavado (mismo nivel de stock hace semanas). Que enfoque de reposicion es mas inteligente?</t>
+  </si>
+  <si>
+    <t>“Sumemos un poco más del mismo para darle más presencia y ver si se mueve por volumen.”</t>
+  </si>
+  <si>
+    <t>“Dejémoslo como está y sigamos con el pedido habitual, sin meternos en ese producto hoy.”</t>
+  </si>
+  <si>
+    <t>“Antes de reponer, ubiquemos qué lo frena: salida, precio o ubicación, y definimos un ajuste puntual.”</t>
+  </si>
+  <si>
+    <t>“Esto lo compraste mal; así no se trabaja. La próxima pedime solo lo que rota bien.”</t>
+  </si>
+  <si>
+    <t>“Después lo vemos; por ahora sigamos con otra cosa y cerramos el pedido como siempre hoy.”</t>
+  </si>
+  <si>
+    <t>E6</t>
+  </si>
+  <si>
+    <t>Despues de asegurar reposicion, queres entender por que el cliente compra una categoria a otro proveedor. Que pregunta cuida mejor el vinculo?</t>
+  </si>
+  <si>
+    <t>¿Por qué le comprás a otro si yo también te lo puedo vender hoy mismo acá?</t>
+  </si>
+  <si>
+    <t>¿Ese proveedor te da mejor precio? Si no, te conviene comprarme a mí esta vez hoy.</t>
+  </si>
+  <si>
+    <t>¿Qué te gusta más de ese proveedor: precio, entrega o surtido, para entender tu elección mejor?</t>
+  </si>
+  <si>
+    <t>¿Qué te viene resolviendo ese proveedor en esa categoría, para ver cómo me ajusto yo también?</t>
+  </si>
+  <si>
+    <t>Si preferís, no lo hablamos ahora; seguimos con lo de siempre y cerramos tranquilo hoy acá.</t>
+  </si>
+  <si>
+    <t>E7</t>
+  </si>
+  <si>
+    <t>Ves que el precio en gondola de tu producto esta muy por encima de lo habitual del barrio. Que accion es mas alineada al foco en venta?</t>
+  </si>
+  <si>
+    <t>“Lo dejo como está; el precio lo maneja el local y no me meto con eso hoy.”</t>
+  </si>
+  <si>
+    <t>“Lo bajo yo ahora mismo para que se venda, y después vemos el resto cuando haya tiempo.”</t>
+  </si>
+  <si>
+    <t>“Ese precio está mal; así no vas a vender” y lo marco como error sin preguntar contexto.</t>
+  </si>
+  <si>
+    <t>“Llevemos más cantidad igual para compensar” y después vemos si se mueve con volumen ahí.</t>
+  </si>
+  <si>
+    <t>“¿A cuánto lo estás vendiendo hoy?” para entender el punto de partida antes de proponer ajuste.</t>
+  </si>
+  <si>
+    <t>E8</t>
+  </si>
+  <si>
+    <t>Que tema NO deberias abrir vos durante la recorrida si el cliente no lo menciona?</t>
+  </si>
+  <si>
+    <t>Faltantes de stock o quiebres en góndola que puedan estar frenando ventas hoy.</t>
+  </si>
+  <si>
+    <t>Productos que no rotan o están clavados y ocupan espacio sin aportar margen.</t>
+  </si>
+  <si>
+    <t>Precio visible en góndola si está fuera de rango para el barrio o la rotación.</t>
+  </si>
+  <si>
+    <t>Problemas de logística o entregas como tema principal, sin señal previa del cliente.</t>
+  </si>
+  <si>
+    <t>Productos de otros proveedores en la categoría y cómo conviven con tus frentes actuales.</t>
+  </si>
+  <si>
+    <t>E9</t>
+  </si>
+  <si>
+    <t>Tenes 3 minutos para recorrer. Que chequeo te da mas informacion para armar un pedido base con sentido?</t>
+  </si>
+  <si>
+    <t>Chequear faltantes y quiebres de lo que más rota para armar la reposición base del local hoy.</t>
+  </si>
+  <si>
+    <t>Detectar qué productos están clavados y qué conviene pausar, sin mirar el resto del recorrido.</t>
+  </si>
+  <si>
+    <t>Revisar precios visibles en góndola para ver desvíos, sin mirar rotación ni faltantes del local.</t>
+  </si>
+  <si>
+    <t>Abrir por entregas y servicio para ver reclamos, antes de revisar stock en punto de venta.</t>
+  </si>
+  <si>
+    <t>Mirar el triángulo: vendido, no vendido y competencia, para armar base y una oportunidad real.</t>
+  </si>
+  <si>
+    <t>E10</t>
+  </si>
+  <si>
+    <t>Cual frase propone reposicion base sin marear al cliente?</t>
+  </si>
+  <si>
+    <t>Si querés, decime qué te falta hoy y lo armamos rápido con eso.</t>
+  </si>
+  <si>
+    <t>Te muestro algunas opciones y vos vas eligiendo de a poco lo que prefieras.</t>
+  </si>
+  <si>
+    <t>Veo que de X estás corto; para cubrir la semana te propongo reponer 5 cajas hoy.</t>
+  </si>
+  <si>
+    <t>Hoy te recomiendo sumar algunos lanzamientos que están saliendo y probarlos esta semana.</t>
+  </si>
+  <si>
+    <t>Necesito que hoy el pedido sea más grande para que me cierre bien la visita. Respuestas + explicacion (por que es correcta)</t>
   </si>
 </sst>
 </file>
@@ -761,7 +761,7 @@
         <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -790,7 +790,7 @@
         <v>44</v>
       </c>
       <c r="I6" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -848,7 +848,7 @@
         <v>58</v>
       </c>
       <c r="I8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -877,7 +877,7 @@
         <v>65</v>
       </c>
       <c r="I9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -906,7 +906,7 @@
         <v>72</v>
       </c>
       <c r="I10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -935,7 +935,7 @@
         <v>79</v>
       </c>
       <c r="I11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
